--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104460_W1.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104460_W1.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>J. JACKSON</t>
+          <t>J. AXEL GUDMUNDSSON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5579</v>
+        <v>5.4099</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9873</v>
+        <v>1.6277</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5705</v>
+        <v>3.7822</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1484</v>
+        <v>5.1846</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.8095</v>
+        <v>1.2401</v>
       </c>
       <c r="I2" t="n">
-        <v>4.9578</v>
+        <v>3.9445</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6618</v>
+        <v>4.3494</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.8006</v>
+        <v>1.7582</v>
       </c>
       <c r="L2" t="n">
-        <v>3.4623</v>
+        <v>2.5912</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4866</v>
+        <v>0.8352000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.0089</v>
+        <v>-0.518</v>
       </c>
       <c r="O2" t="n">
-        <v>1.4955</v>
+        <v>1.3532</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2683</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-3.4145</v>
       </c>
       <c r="R2" t="n">
-        <v>2.2683</v>
+        <v>2.7316</v>
       </c>
       <c r="S2" t="n">
-        <v>1.009</v>
+        <v>0.7504</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6866</v>
+        <v>-0.0097</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3224</v>
+        <v>0.7602</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.8678</v>
+        <v>0.1578</v>
       </c>
       <c r="W2" t="n">
-        <v>1.639</v>
+        <v>0.7025</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.5068</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. AXEL GUDMUNDSSON</t>
+          <t>J. JACKSON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.6332</v>
+        <v>5.3406</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5828</v>
+        <v>4.593</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0504</v>
+        <v>0.7477</v>
       </c>
       <c r="G3" t="n">
-        <v>5.1742</v>
+        <v>3.1418</v>
       </c>
       <c r="H3" t="n">
-        <v>1.2292</v>
+        <v>-1.8094</v>
       </c>
       <c r="I3" t="n">
-        <v>3.945</v>
+        <v>4.9512</v>
       </c>
       <c r="J3" t="n">
-        <v>4.3731</v>
+        <v>2.6224</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7663</v>
+        <v>-0.8176</v>
       </c>
       <c r="L3" t="n">
-        <v>2.6068</v>
+        <v>3.44</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8011</v>
+        <v>0.5194</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5371</v>
+        <v>-0.9918</v>
       </c>
       <c r="O3" t="n">
-        <v>1.3382</v>
+        <v>1.5112</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.6805</v>
+        <v>2.2763</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.4025</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.722</v>
+        <v>2.2763</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0212</v>
+        <v>0.7828000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0948</v>
+        <v>0.3363</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0736</v>
+        <v>0.4465</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1607</v>
+        <v>-0.8603</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7071</v>
+        <v>1.6342</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.5463</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="4">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2334</v>
+        <v>3.8471</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7761</v>
+        <v>-1.0347</v>
       </c>
       <c r="F4" t="n">
-        <v>5.0094</v>
+        <v>4.8819</v>
       </c>
       <c r="G4" t="n">
-        <v>1.455</v>
+        <v>1.4351</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3262</v>
+        <v>3.3123</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.8712</v>
+        <v>-1.8772</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.2624</v>
+        <v>-0.3025</v>
       </c>
       <c r="K4" t="n">
-        <v>2.8084</v>
+        <v>2.7816</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.0708</v>
+        <v>-3.0841</v>
       </c>
       <c r="M4" t="n">
-        <v>1.7174</v>
+        <v>1.7375</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5178</v>
+        <v>0.5306</v>
       </c>
       <c r="O4" t="n">
-        <v>1.1995</v>
+        <v>1.2069</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S4" t="n">
-        <v>1.0298</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4597</v>
+        <v>0.2481</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5701000000000001</v>
+        <v>0.4127</v>
       </c>
       <c r="V4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3429</v>
+        <v>2.9576</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9207</v>
+        <v>0.6531</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4222</v>
+        <v>2.3045</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7568</v>
+        <v>1.7704</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0505</v>
+        <v>-0.0489</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8073</v>
+        <v>1.8194</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5602</v>
+        <v>2.5434</v>
       </c>
       <c r="K5" t="n">
-        <v>1.7765</v>
+        <v>1.7614</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7837</v>
+        <v>0.782</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8034</v>
+        <v>-0.7729</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.827</v>
+        <v>-1.8103</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0237</v>
+        <v>1.0374</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5878</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5349</v>
+        <v>1.1463</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8953</v>
+        <v>0.6639</v>
       </c>
       <c r="U5" t="n">
-        <v>0.6395999999999999</v>
+        <v>0.4824</v>
       </c>
       <c r="V5" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8678</v>
+        <v>0.8603</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7712</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. DIEZ</t>
+          <t>J. SAMUELS JR</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7985</v>
+        <v>1.9474</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.8472</v>
+        <v>0.8368</v>
       </c>
       <c r="F6" t="n">
-        <v>4.6457</v>
+        <v>1.1106</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1297</v>
+        <v>1.7385</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8136</v>
+        <v>0.5315</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.9433</v>
+        <v>1.2069</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.9226</v>
+        <v>1.4062</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0044</v>
+        <v>1.4511</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.9269</v>
+        <v>-0.0449</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7929</v>
+        <v>0.3322</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1908</v>
+        <v>-0.9196</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9837</v>
+        <v>1.2518</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9073</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>3.1757</v>
+        <v>1.1382</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9282</v>
+        <v>1.1893</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2511</v>
+        <v>0.4596</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6771</v>
+        <v>0.7297</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>1.2472</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. SAMUELS JR</t>
+          <t>L. MEINDL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7523</v>
+        <v>1.6183</v>
       </c>
       <c r="E7" t="n">
-        <v>0.797</v>
+        <v>0.1309</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9553</v>
+        <v>1.4874</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7349</v>
+        <v>-1.541</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5354</v>
+        <v>0.15</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1995</v>
+        <v>-1.691</v>
       </c>
       <c r="J7" t="n">
-        <v>1.4248</v>
+        <v>-1.9024</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4648</v>
+        <v>1.4577</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.04</v>
+        <v>-3.3601</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3102</v>
+        <v>0.3614</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9294</v>
+        <v>-1.3077</v>
       </c>
       <c r="O7" t="n">
-        <v>1.2396</v>
+        <v>1.6691</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1342</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9908</v>
+        <v>1.1185</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3871</v>
+        <v>0.3388</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6037</v>
+        <v>0.7798</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1607</v>
+        <v>2.7237</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2534</v>
+        <v>3.9709</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0927</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. NETO</t>
+          <t>D. DIEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.6708</v>
+        <v>1.3017</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1396</v>
+        <v>-3.0986</v>
       </c>
       <c r="F8" t="n">
-        <v>1.5312</v>
+        <v>4.4002</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.6621</v>
+        <v>-1.1316</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0678</v>
+        <v>0.8265</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.73</v>
+        <v>-1.958</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.2276</v>
+        <v>-1.9507</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1314</v>
+        <v>0.9997</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.3591</v>
+        <v>-2.9505</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5655</v>
+        <v>0.8192</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0636</v>
+        <v>-0.1733</v>
       </c>
       <c r="O8" t="n">
-        <v>0.6291</v>
+        <v>0.9925</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1342</v>
+        <v>3.1868</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9869</v>
+        <v>0.4332</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1553</v>
+        <v>0.039</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1685</v>
+        <v>0.3942</v>
       </c>
       <c r="V8" t="n">
-        <v>2.3461</v>
+        <v>1.0895</v>
       </c>
       <c r="W8" t="n">
-        <v>2.3461</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. MEINDL</t>
+          <t>R. NETO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5365</v>
+        <v>1.0477</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8129</v>
+        <v>-0.7145</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3494</v>
+        <v>1.7622</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5229</v>
+        <v>-1.6711</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1618</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6847</v>
+        <v>-1.7372</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.8522</v>
+        <v>-2.245</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4852</v>
+        <v>0.1239</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.3374</v>
+        <v>-2.3689</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3293</v>
+        <v>0.574</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3234</v>
+        <v>-0.0578</v>
       </c>
       <c r="O9" t="n">
-        <v>1.6528</v>
+        <v>0.6317</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>0.008200000000000001</v>
+        <v>0.382</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6775</v>
+        <v>0.3319</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6856</v>
+        <v>0.0501</v>
       </c>
       <c r="V9" t="n">
-        <v>2.7317</v>
+        <v>2.3367</v>
       </c>
       <c r="W9" t="n">
-        <v>3.9851</v>
+        <v>2.3367</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2534</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2983</v>
+        <v>0.9302</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4675</v>
+        <v>-0.0444</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7658</v>
+        <v>0.9746</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.31</v>
+        <v>-0.3011</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1314</v>
+        <v>-0.1239</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1786</v>
+        <v>-0.1772</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1585</v>
+        <v>0.1579</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1212</v>
+        <v>0.1207</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4685</v>
+        <v>-0.459</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2159</v>
+        <v>-0.2144</v>
       </c>
       <c r="P10" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6581</v>
+        <v>-0.0466</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6261</v>
+        <v>-0.2023</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0321</v>
+        <v>0.1557</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0307</v>
+        <v>0.06759999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0672</v>
+        <v>-0.0677</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0979</v>
+        <v>0.1353</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0133</v>
+        <v>0.0152</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0213</v>
+        <v>-0.0193</v>
       </c>
       <c r="J11" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.0717</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0346</v>
+        <v>0.0345</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0586</v>
+        <v>-0.0565</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0487</v>
+        <v>-0.0174</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1391</v>
+        <v>-0.1394</v>
       </c>
       <c r="U11" t="n">
-        <v>0.09039999999999999</v>
+        <v>0.122</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.9554</v>
+        <v>-0.9816</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2334</v>
+        <v>-0.2411</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.722</v>
+        <v>-0.7405</v>
       </c>
       <c r="G12" t="n">
-        <v>0.658</v>
+        <v>0.655</v>
       </c>
       <c r="H12" t="n">
-        <v>0.1862</v>
+        <v>0.1812</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0448</v>
+        <v>0.0377</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0448</v>
+        <v>0.0377</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6132</v>
+        <v>0.6173</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1414</v>
+        <v>0.1435</v>
       </c>
       <c r="O12" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1086</v>
+        <v>-0.1405</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2782</v>
+        <v>-0.2788</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1697</v>
+        <v>0.1383</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.0863</v>
+        <v>-1.9669</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.6176</v>
+        <v>-2.6813</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5312</v>
+        <v>0.7143</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3346</v>
+        <v>-0.3352</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9797</v>
+        <v>-0.9848</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6451</v>
+        <v>0.6497000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.6437</v>
+        <v>-1.6567</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.7184</v>
+        <v>-1.7312</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M13" t="n">
-        <v>1.3091</v>
+        <v>1.3215</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7387</v>
+        <v>0.7463</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3675</v>
+        <v>0.4773</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1603</v>
+        <v>0.1136</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2072</v>
+        <v>0.3637</v>
       </c>
       <c r="V13" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.3461</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>20.8128</v>
+        <v>21.5196</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.3945000000000003</v>
+        <v>-0.04079999999999906</v>
       </c>
       <c r="F14" t="n">
-        <v>21.207</v>
+        <v>21.5604</v>
       </c>
       <c r="G14" t="n">
-        <v>8.981299999999997</v>
+        <v>8.960599999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3837</v>
+        <v>3.3753</v>
       </c>
       <c r="I14" t="n">
-        <v>5.597399999999999</v>
+        <v>5.585599999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>3.386700000000002</v>
+        <v>3.131399999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>8.118599999999997</v>
+        <v>7.977699999999998</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.732199999999999</v>
+        <v>-4.846399999999998</v>
       </c>
       <c r="M14" t="n">
-        <v>5.5948</v>
+        <v>5.8293</v>
       </c>
       <c r="N14" t="n">
-        <v>-4.734900000000001</v>
+        <v>-4.6027</v>
       </c>
       <c r="O14" t="n">
-        <v>10.3299</v>
+        <v>10.4319</v>
       </c>
       <c r="P14" t="n">
-        <v>3.4023</v>
+        <v>3.414299999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-17.0125</v>
+        <v>-17.0725</v>
       </c>
       <c r="R14" t="n">
-        <v>20.415</v>
+        <v>20.4869</v>
       </c>
       <c r="S14" t="n">
-        <v>6.018699999999999</v>
+        <v>6.7361</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1797</v>
+        <v>1.900999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>4.838800000000001</v>
+        <v>4.8353</v>
       </c>
       <c r="V14" t="n">
-        <v>2.4103</v>
+        <v>2.408299999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>12.0519</v>
+        <v>11.9991</v>
       </c>
       <c r="X14" t="n">
-        <v>-9.641500000000001</v>
+        <v>-9.590900000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ</t>
+          <t>P. BUSQUETS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9322</v>
+        <v>2.2471</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8137</v>
+        <v>1.5639</v>
       </c>
       <c r="F15" t="n">
-        <v>1.1185</v>
+        <v>0.6832</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7236</v>
+        <v>3.9274</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7445</v>
+        <v>3.3612</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0209</v>
+        <v>0.5662</v>
       </c>
       <c r="J15" t="n">
-        <v>0.488</v>
+        <v>3.2646</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0607</v>
+        <v>4.3674</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.5727</v>
+        <v>-1.1029</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2356</v>
+        <v>0.6629</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3162</v>
+        <v>-1.0062</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5518999999999999</v>
+        <v>1.6691</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4537</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1342</v>
+        <v>-4.5526</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4984</v>
+        <v>-0.8106</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8861</v>
+        <v>-0.5742</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3877</v>
+        <v>-0.2364</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2534</v>
+        <v>1.6342</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3461</v>
+        <v>3.4262</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0927</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>P. BUSQUETS</t>
+          <t>J. FERNANDEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2781</v>
+        <v>1.6762</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0489</v>
+        <v>0.9013</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2291</v>
+        <v>0.775</v>
       </c>
       <c r="G16" t="n">
-        <v>3.9392</v>
+        <v>0.7332</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3768</v>
+        <v>1.7489</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5625</v>
+        <v>-1.0157</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3113</v>
+        <v>0.4719</v>
       </c>
       <c r="K16" t="n">
-        <v>4.4016</v>
+        <v>2.0512</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.0903</v>
+        <v>-1.5793</v>
       </c>
       <c r="M16" t="n">
-        <v>0.628</v>
+        <v>0.2613</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0248</v>
+        <v>-0.3023</v>
       </c>
       <c r="O16" t="n">
-        <v>1.6528</v>
+        <v>0.5636</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.4952</v>
+        <v>0.4553</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.5367</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0415</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.805</v>
+        <v>-0.7594</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.1644</v>
+        <v>-0.7692</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6405999999999999</v>
+        <v>0.0097</v>
       </c>
       <c r="V16" t="n">
-        <v>1.639</v>
+        <v>1.2472</v>
       </c>
       <c r="W16" t="n">
-        <v>3.4387</v>
+        <v>2.3367</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.7997</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. MARTINEZ</t>
+          <t>M. SUSINSKAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7917</v>
+        <v>0.1613</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1934</v>
+        <v>-0.0772</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9851</v>
+        <v>0.2385</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.1042</v>
+        <v>-0.3521</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3739</v>
+        <v>0.9243</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7302999999999999</v>
+        <v>-1.2763</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0608</v>
+        <v>-0.7436</v>
       </c>
       <c r="K17" t="n">
-        <v>1.4373</v>
+        <v>0.7239</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.4981</v>
+        <v>-1.4676</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0434</v>
+        <v>0.3916</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.8112</v>
+        <v>0.2003</v>
       </c>
       <c r="O17" t="n">
-        <v>0.7678</v>
+        <v>0.1912</v>
       </c>
       <c r="P17" t="n">
-        <v>2.0415</v>
+        <v>1.3658</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0415</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>0.7864</v>
+        <v>-0.3077</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4779</v>
+        <v>-0.4231</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3085</v>
+        <v>0.1154</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.5447</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6105</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3214</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SUSINSKAS</t>
+          <t>S. HOLLANDERS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.251</v>
+        <v>-0.1016</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1717</v>
+        <v>-0.1394</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0793</v>
+        <v>0.0378</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3674</v>
+        <v>-0.0144</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9147</v>
+        <v>-0.0144</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2821</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.7335</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7272999999999999</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.4608</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3661</v>
+        <v>-0.0144</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1874</v>
+        <v>-0.0144</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1787</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1963</v>
+        <v>-0.0871</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1875</v>
+        <v>-0.1394</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.0523</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. HOLLANDERS</t>
+          <t>S. MARTINEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1341</v>
+        <v>-0.2097</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1391</v>
+        <v>-0.9185</v>
       </c>
       <c r="F19" t="n">
-        <v>0.005</v>
+        <v>0.7087</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0159</v>
+        <v>-1.092</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0159</v>
+        <v>-0.3652</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>-0.7268</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.0742</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.4307</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-1.5048</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0159</v>
+        <v>-1.0179</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.0159</v>
+        <v>-1.7959</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>0.778</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.0487</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.0487</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.1183</v>
+        <v>-0.2347</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1391</v>
+        <v>-0.2281</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0209</v>
+        <v>-0.0066</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.9317</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.6162</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. MARIC</t>
+          <t>P. VILDOZA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.473</v>
+        <v>-0.5901</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6861</v>
+        <v>-2.4484</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2132</v>
+        <v>1.8583</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.6001</v>
+        <v>0.3807</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9307</v>
+        <v>0.2241</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3306</v>
+        <v>0.1566</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4461</v>
+        <v>-0.1544</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.5208</v>
+        <v>0.1961</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0746</v>
+        <v>-0.3505</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.154</v>
+        <v>0.5351</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4099</v>
+        <v>0.028</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2559</v>
+        <v>0.5071</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.2763</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.3658</v>
       </c>
       <c r="S20" t="n">
-        <v>0.8057</v>
+        <v>-0.605</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4386</v>
+        <v>-0.5625</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3672</v>
+        <v>-0.0425</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3214</v>
+        <v>0.5447</v>
       </c>
       <c r="W20" t="n">
-        <v>0.3214</v>
+        <v>0.5447</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. VILDOZA</t>
+          <t>N. MARIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4766</v>
+        <v>-0.8347</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.179</v>
+        <v>-0.9333</v>
       </c>
       <c r="F21" t="n">
-        <v>1.7024</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>0.3771</v>
+        <v>-1.5963</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2251</v>
+        <v>-1.9301</v>
       </c>
       <c r="I21" t="n">
-        <v>0.152</v>
+        <v>0.3338</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1304</v>
+        <v>-1.4531</v>
       </c>
       <c r="K21" t="n">
-        <v>0.2109</v>
+        <v>-1.5276</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3413</v>
+        <v>0.0745</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5074</v>
+        <v>-0.1432</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0142</v>
+        <v>-0.4025</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4932</v>
+        <v>0.2593</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.9073</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.361</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4927</v>
+        <v>0.446</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3266</v>
+        <v>0.2042</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1661</v>
+        <v>0.2418</v>
       </c>
       <c r="V21" t="n">
-        <v>0.5463</v>
+        <v>0.3155</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5463</v>
+        <v>0.3155</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2175</v>
+        <v>-0.915</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2744</v>
+        <v>-2.3267</v>
       </c>
       <c r="F22" t="n">
-        <v>1.057</v>
+        <v>1.4117</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.4739</v>
+        <v>-1.4806</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.6174</v>
+        <v>-2.6247</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1435</v>
+        <v>1.144</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.5851</v>
+        <v>-0.6235000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.923</v>
+        <v>-1.9487</v>
       </c>
       <c r="L22" t="n">
-        <v>1.338</v>
+        <v>1.3252</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.8888</v>
+        <v>-0.8571</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6944</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1945</v>
+        <v>-0.1811</v>
       </c>
       <c r="P22" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4952</v>
+        <v>2.5039</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0631</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6744</v>
+        <v>-0.6741</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3887</v>
+        <v>-0.0774</v>
       </c>
       <c r="V22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4204</v>
+        <v>-1.8137</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6211</v>
+        <v>-2.2822</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2008</v>
+        <v>0.4685</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.5821</v>
+        <v>-0.5757</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1269</v>
+        <v>0.1318</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.709</v>
+        <v>-0.7075</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.6522</v>
+        <v>-0.663</v>
       </c>
       <c r="K23" t="n">
-        <v>0.8832</v>
+        <v>0.8791</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M23" t="n">
-        <v>0.0701</v>
+        <v>0.0873</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7563</v>
+        <v>-0.7472</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8264</v>
+        <v>0.8345</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3846</v>
+        <v>-0.7828000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8347</v>
+        <v>-0.4811</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5498</v>
+        <v>-0.3017</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.6691</v>
+        <v>-3.2773</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6102</v>
+        <v>-1.9985</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0589</v>
+        <v>-1.2789</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.9377</v>
+        <v>-1.9405</v>
       </c>
       <c r="H24" t="n">
-        <v>0.2481</v>
+        <v>0.2525</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.1858</v>
+        <v>-2.193</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7738</v>
+        <v>-0.7949000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>1.1775</v>
+        <v>1.1721</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.9513</v>
+        <v>-1.967</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.1639</v>
+        <v>-1.1457</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>0.4954</v>
+        <v>-0.1092</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1785</v>
+        <v>-0.1745</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3169</v>
+        <v>0.0653</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2534</v>
+        <v>1.2472</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.7645</v>
+        <v>-4.0785</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.8582</v>
+        <v>-2.518</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.9063</v>
+        <v>-1.5605</v>
       </c>
       <c r="G25" t="n">
-        <v>-1.6483</v>
+        <v>-1.6432</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.1125</v>
+        <v>-1.1115</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.5357</v>
+        <v>-0.5316</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.8893</v>
+        <v>-0.8988</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.2149</v>
+        <v>-0.2208</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.759</v>
+        <v>-0.7444</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.8976</v>
+        <v>-0.8907</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P25" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.2899</v>
+        <v>-0.6238</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.8347</v>
+        <v>-0.4811</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4552</v>
+        <v>-0.1427</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.5068</v>
+        <v>-2.4945</v>
       </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-2.5068</v>
+        <v>-2.4945</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-12.9106</v>
+        <v>-12.2968</v>
       </c>
       <c r="E26" t="n">
-        <v>-10.6798</v>
+        <v>-10.3834</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.2308</v>
+        <v>-1.9134</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.2917</v>
+        <v>-5.3072</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.9695</v>
+        <v>-3.972</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.3222</v>
+        <v>-1.3353</v>
       </c>
       <c r="J26" t="n">
-        <v>-4.1229</v>
+        <v>-4.1603</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.5047</v>
+        <v>-2.5208</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.6181</v>
+        <v>-1.6395</v>
       </c>
       <c r="M26" t="n">
-        <v>-1.1689</v>
+        <v>-1.1469</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.4648</v>
+        <v>-1.4511</v>
       </c>
       <c r="O26" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P26" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="Q26" t="n">
-        <v>-5.6708</v>
+        <v>-5.6908</v>
       </c>
       <c r="R26" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.2579</v>
+        <v>-0.6238</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8861</v>
+        <v>-0.5323</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.3717</v>
+        <v>-0.0915</v>
       </c>
       <c r="V26" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-20.8128</v>
+        <v>-20.0328</v>
       </c>
       <c r="E27" t="n">
-        <v>-21.207</v>
+        <v>-21.5604</v>
       </c>
       <c r="F27" t="n">
-        <v>0.3943999999999996</v>
+        <v>1.527499999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>-8.981400000000001</v>
+        <v>-8.960700000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>-3.383800000000001</v>
+        <v>-3.3751</v>
       </c>
       <c r="I27" t="n">
-        <v>-5.5974</v>
+        <v>-5.5856</v>
       </c>
       <c r="J27" t="n">
-        <v>-5.594799999999999</v>
+        <v>-5.8293</v>
       </c>
       <c r="K27" t="n">
-        <v>4.735100000000001</v>
+        <v>4.602600000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>-10.3298</v>
+        <v>-10.4318</v>
       </c>
       <c r="M27" t="n">
-        <v>-3.3867</v>
+        <v>-3.1314</v>
       </c>
       <c r="N27" t="n">
-        <v>-8.1189</v>
+        <v>-7.977500000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>4.7323</v>
+        <v>4.846299999999999</v>
       </c>
       <c r="P27" t="n">
-        <v>-3.4025</v>
+        <v>-3.4144</v>
       </c>
       <c r="Q27" t="n">
-        <v>-20.415</v>
+        <v>-20.4869</v>
       </c>
       <c r="R27" t="n">
-        <v>17.0125</v>
+        <v>17.0724</v>
       </c>
       <c r="S27" t="n">
-        <v>-6.0187</v>
+        <v>-5.2496</v>
       </c>
       <c r="T27" t="n">
-        <v>-4.8386</v>
+        <v>-4.8354</v>
       </c>
       <c r="U27" t="n">
-        <v>-1.1797</v>
+        <v>-0.4143</v>
       </c>
       <c r="V27" t="n">
-        <v>-2.4103</v>
+        <v>-2.408199999999999</v>
       </c>
       <c r="W27" t="n">
-        <v>9.641500000000001</v>
+        <v>9.5908</v>
       </c>
       <c r="X27" t="n">
-        <v>-12.0517</v>
+        <v>-11.9992</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104460_W1.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104460_W1.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-9.590900000000001</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-2.4945</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104460_W1.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-11.9992</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
